--- a/patients_updated.xlsx
+++ b/patients_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BEVAN\Desktop\health_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B20F1308-5D49-4099-A926-2B4BD5895EB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1341917-F07E-4078-BF03-7C24A834EBC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11265" windowHeight="4170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -851,7 +851,7 @@
         <v>97167817237</v>
       </c>
       <c r="I10">
-        <v>917</v>
+        <v>9117</v>
       </c>
     </row>
   </sheetData>
